--- a/AtchisonRegime/Outputs/Aust/ASX300_Info_Tech/df_regTrendSummaryASX300_Info_Tech.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300_Info_Tech/df_regTrendSummaryASX300_Info_Tech.xlsx
@@ -1462,13 +1462,13 @@
         <v>45351</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2043649654773743</v>
+        <v>0.09458190277135792</v>
       </c>
     </row>
   </sheetData>
